--- a/data/Diessenhofen/investment_decision/Willisdorf_MFH_until_2004_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Willisdorf_MFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>27.35034017740671</v>
+        <v>17.55346630252913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>11911.34523742506</v>
       </c>
       <c r="F2" t="n">
-        <v>27.59062721551673</v>
+        <v>17.40749886674454</v>
       </c>
       <c r="G2" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="H2" t="n">
-        <v>28.01056023365575</v>
+        <v>14.33043904516791</v>
       </c>
       <c r="I2" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="J2" t="n">
-        <v>27.94019287558329</v>
+        <v>16.98727798935817</v>
       </c>
       <c r="K2" t="n">
         <v>11911.34523742506</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>32.11180479773325</v>
+        <v>21.6913635172499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>11911.34523742506</v>
       </c>
       <c r="F3" t="n">
-        <v>32.30987706718756</v>
+        <v>20.37438309602411</v>
       </c>
       <c r="G3" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="H3" t="n">
-        <v>32.9577211275645</v>
+        <v>19.30719374061242</v>
       </c>
       <c r="I3" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="J3" t="n">
-        <v>32.89929067972597</v>
+        <v>17.00303846967105</v>
       </c>
       <c r="K3" t="n">
         <v>11911.34523742506</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86636746666667</v>
+        <v>43.90923937613216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>11911.34523742506</v>
       </c>
       <c r="F4" t="n">
-        <v>34.97887869438834</v>
+        <v>44.18815600466552</v>
       </c>
       <c r="G4" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="H4" t="n">
-        <v>35.62441152472505</v>
+        <v>43.80760481439877</v>
       </c>
       <c r="I4" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="J4" t="n">
-        <v>35.34781251512063</v>
+        <v>45.05007371091529</v>
       </c>
       <c r="K4" t="n">
         <v>11911.34523742506</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>37.12504409635688</v>
+        <v>48.20156609721347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>11911.34523742506</v>
       </c>
       <c r="F5" t="n">
-        <v>37.03895561385181</v>
+        <v>48.38624696910931</v>
       </c>
       <c r="G5" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="H5" t="n">
-        <v>37.86152993857478</v>
+        <v>48.19737892378956</v>
       </c>
       <c r="I5" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="J5" t="n">
-        <v>37.86152993857478</v>
+        <v>48.09552412668744</v>
       </c>
       <c r="K5" t="n">
         <v>11911.34523742506</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>37.12504409635688</v>
+        <v>48.20156609721347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>11911.34523742506</v>
       </c>
       <c r="F6" t="n">
-        <v>37.03895561385181</v>
+        <v>48.38624696910931</v>
       </c>
       <c r="G6" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="H6" t="n">
-        <v>37.86152993857479</v>
+        <v>48.19737892378956</v>
       </c>
       <c r="I6" t="n">
         <v>11911.34523742506</v>
       </c>
       <c r="J6" t="n">
-        <v>37.86152993857478</v>
+        <v>48.09552412668744</v>
       </c>
       <c r="K6" t="n">
         <v>11911.34523742506</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>10.43259270636897</v>
+        <v>12.37217530562769</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10.43259270636897</v>
+        <v>12.37217530562769</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>13.84682123761513</v>
+        <v>16.4211624664382</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13.84682123761513</v>
+        <v>16.4211624664382</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>15.33776871321643</v>
+        <v>18.1893004603964</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>15.33776871321643</v>
+        <v>18.1893004603964</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>16.11270887451118</v>
+        <v>19.10831415112133</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>16.11270887451118</v>
+        <v>19.10831415112133</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>17.8670178561376</v>
+        <v>21.18877668539326</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>16.56458361613244</v>
+        <v>19.64419949399592</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>16.56458361613244</v>
+        <v>19.64419949399592</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058823</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058823</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058823</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.003691733025882353</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003911016838669706</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003905643695139992</v>
+        <v>0.003384088607058823</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.003980713212769993</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.003966766998337957</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003911016838669706</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.003905643695139992</v>
+        <v>0.003384088607058823</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.003980713212769993</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003966766998337957</v>
+        <v>0.003384088607058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05851124452125075</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05665431699511659</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="G17" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05058077892908287</v>
+        <v>0.1898964852538607</v>
       </c>
       <c r="I17" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05112856437756899</v>
+        <v>0.1906015234191962</v>
       </c>
       <c r="K17" t="n">
         <v>0.5491452875999999</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05851124452125075</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05665431699511659</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="G18" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05058077892908285</v>
+        <v>0.1898964852538607</v>
       </c>
       <c r="I18" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05112856437756901</v>
+        <v>0.196123317</v>
       </c>
       <c r="K18" t="n">
         <v>0.5491452875999999</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05851124452125075</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05665431699511659</v>
+        <v>0.1797797072499999</v>
       </c>
       <c r="G19" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05058077892908287</v>
+        <v>0.1898964852538607</v>
       </c>
       <c r="I19" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05112856437756899</v>
+        <v>0.196123317</v>
       </c>
       <c r="K19" t="n">
         <v>0.5491452875999999</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02573192414134368</v>
+        <v>0.1003620463450207</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02630282064137591</v>
+        <v>0.1005377914673598</v>
       </c>
       <c r="G20" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0183266843931885</v>
+        <v>0.08323642266803841</v>
       </c>
       <c r="I20" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01980846967659207</v>
+        <v>0.08805551391215732</v>
       </c>
       <c r="K20" t="n">
         <v>0.5491452875999999</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02573192414134368</v>
+        <v>0.1003620463450207</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02630282064137591</v>
+        <v>0.1005377914673598</v>
       </c>
       <c r="G21" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0183266843931885</v>
+        <v>0.08323642266803841</v>
       </c>
       <c r="I21" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01980846967659207</v>
+        <v>0.08253372033135357</v>
       </c>
       <c r="K21" t="n">
         <v>0.5491452875999999</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01404322190497931</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.0137441213146092</v>
       </c>
       <c r="G30" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.0306777010379256</v>
       </c>
       <c r="I30" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.02853554956391743</v>
       </c>
       <c r="K30" t="n">
         <v>0.5491452875999999</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.01634360974999999</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>0.5491452875999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.01585262409180584</v>
       </c>
       <c r="G31" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.0306777010379256</v>
       </c>
       <c r="I31" t="n">
         <v>0.5491452875999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02853554956391743</v>
       </c>
       <c r="K31" t="n">
         <v>0.5491452875999999</v>
@@ -2142,13 +2142,13 @@
         <v>26.13710613145126</v>
       </c>
       <c r="H46" t="n">
-        <v>23.79250115251406</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>23.53137639298681</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>23.79250115251406</v>
       </c>
       <c r="K46" t="n">
         <v>23.53137639298681</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.8981783983404531</v>
+        <v>0.9069302225185337</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8936220378571167</v>
+        <v>0.8980836321409111</v>
       </c>
       <c r="G52" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8854502329821167</v>
+        <v>0.7796241733087459</v>
       </c>
       <c r="I52" t="n">
         <v>1.189501949278947</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8336218767390177</v>
+        <v>0.8523736360375385</v>
       </c>
       <c r="K52" t="n">
         <v>1.189501949278947</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.8981783983404531</v>
+        <v>0.9069302225185337</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8936220378571167</v>
+        <v>0.8980836321409111</v>
       </c>
       <c r="G53" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8854502329821167</v>
+        <v>0.7830519164492485</v>
       </c>
       <c r="I53" t="n">
         <v>1.796220345658749</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8336218767390177</v>
+        <v>0.87543720213295</v>
       </c>
       <c r="K53" t="n">
         <v>1.796220345658749</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.9489441236392852</v>
+        <v>0.9555168592907778</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F54" t="n">
-        <v>0.947098076070195</v>
+        <v>0.9553665175743103</v>
       </c>
       <c r="G54" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9468979364720405</v>
+        <v>0.8473680067420754</v>
       </c>
       <c r="I54" t="n">
         <v>2.148787262730079</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8892776565030818</v>
+        <v>0.9489826950631127</v>
       </c>
       <c r="K54" t="n">
         <v>2.148787262730079</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.9271406178740232</v>
+        <v>0.9251757563353763</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9249863203034117</v>
+        <v>0.9251757563353762</v>
       </c>
       <c r="G55" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9247240437899085</v>
+        <v>0.9258273109926386</v>
       </c>
       <c r="I55" t="n">
         <v>2.3737339580315</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9255005958679989</v>
+        <v>0.92572993971591</v>
       </c>
       <c r="K55" t="n">
         <v>2.3737339580315</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.9271406178740232</v>
+        <v>0.9251757563353765</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9249863203034117</v>
+        <v>0.9251757563353763</v>
       </c>
       <c r="G56" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9247240437899085</v>
+        <v>0.9223995678521359</v>
       </c>
       <c r="I56" t="n">
         <v>2.527143141893183</v>
       </c>
       <c r="J56" t="n">
-        <v>0.925500595867999</v>
+        <v>0.9026663736204985</v>
       </c>
       <c r="K56" t="n">
         <v>2.527143141893183</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5528513302738199</v>
+        <v>0.1364040815755406</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5541699814629649</v>
+        <v>0.1345485817299885</v>
       </c>
       <c r="G64" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5513441859189158</v>
+        <v>0.1374207896676169</v>
       </c>
       <c r="I64" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5484694366666626</v>
+        <v>0.1347338840334556</v>
       </c>
       <c r="K64" t="n">
         <v>3.544942231641141</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.5640672893374091</v>
+        <v>0.1364040815755406</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5666251266697632</v>
+        <v>0.1345485817299885</v>
       </c>
       <c r="G65" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5630315860361272</v>
+        <v>0.1388795758831187</v>
       </c>
       <c r="I65" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5622550339580367</v>
+        <v>0.139709440544672</v>
       </c>
       <c r="K65" t="n">
         <v>3.544942231641141</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.564067289337409</v>
+        <v>0.1364040815755406</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>3.544942231641141</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5666251266697632</v>
+        <v>0.1345485817299885</v>
       </c>
       <c r="G66" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5630315860361271</v>
+        <v>0.1423073190236211</v>
       </c>
       <c r="I66" t="n">
         <v>3.544942231641141</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5622550339580367</v>
+        <v>0.1614703270042011</v>
       </c>
       <c r="K66" t="n">
         <v>3.544942231641141</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.141222270615095</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.141222270615095</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2419024811934115</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2419024811934115</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3213388978958324</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3213388978958324</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3873695300703117</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3873695300703117</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4439962486308079</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.4439962486308079</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="77">
@@ -3289,16 +3289,16 @@
         <v>3.544942231641141</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.1078630540088265</v>
       </c>
       <c r="I77" t="n">
-        <v>0.141222270615095</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J77" t="n">
-        <v>0.06179158707873278</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.141222270615095</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="78">
@@ -3326,16 +3326,16 @@
         <v>3.544942231641141</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.1078630540088265</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2419024811934115</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J78" t="n">
-        <v>0.06179158707873278</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2419024811934115</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="79">
@@ -3363,16 +3363,16 @@
         <v>3.544942231641141</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.1078630540088265</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3213388978958324</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J79" t="n">
-        <v>0.06179158707873278</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3213388978958324</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3873695300703117</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3873695300703117</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4439962486308079</v>
+        <v>3.544942231641141</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4439962486308079</v>
+        <v>3.544942231641141</v>
       </c>
     </row>
     <row r="82">
